--- a/NuevasNotas/Vespertina/Resultados_Auditoria_Notas/Matriz_Marcada_2BV.xlsx
+++ b/NuevasNotas/Vespertina/Resultados_Auditoria_Notas/Matriz_Marcada_2BV.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -58,10 +58,16 @@
       <sz val="12"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -79,24 +85,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="003B82F6"/>
+        <bgColor rgb="003B82F6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00E5E7EB"/>
         <bgColor rgb="00E5E7EB"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F3F4F6"/>
-        <bgColor rgb="00F3F4F6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="8">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -184,11 +184,16 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <bottom style="thin">
+        <color rgb="00CCCCCC"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -220,18 +225,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -599,13 +601,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -617,450 +620,73 @@
       <c r="B1" s="13" t="n"/>
       <c r="C1" s="13" t="n"/>
       <c r="D1" s="13" t="n"/>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="14" t="inlineStr">
-        <is>
-          <t>Curso</t>
-        </is>
-      </c>
-      <c r="B2" s="14" t="inlineStr">
+      <c r="E1" s="13" t="n"/>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="14" t="inlineStr">
+        <is>
+          <t>▶ CURSO: 2BV</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="15" t="inlineStr">
         <is>
           <t>Estudiante</t>
         </is>
       </c>
-      <c r="C2" s="14" t="inlineStr">
+      <c r="B4" s="15" t="inlineStr">
         <is>
           <t>Tipo de Problema</t>
         </is>
       </c>
-      <c r="D2" s="14" t="inlineStr">
-        <is>
-          <t>Detalle de la Discrepancia</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="15" t="inlineStr">
-        <is>
-          <t>2BV</t>
-        </is>
-      </c>
-      <c r="B3" s="16" t="inlineStr">
+      <c r="C4" s="15" t="inlineStr">
+        <is>
+          <t>Materia</t>
+        </is>
+      </c>
+      <c r="D4" s="15" t="inlineStr">
+        <is>
+          <t>Docente</t>
+        </is>
+      </c>
+      <c r="E4" s="15" t="inlineStr">
+        <is>
+          <t>Sistema</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>MEJIA PEÑAFIEL EMELY NAHOMI</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
+      <c r="B5" s="16" t="inlineStr">
         <is>
           <t>⚠️ FALTA EN DOCENTE</t>
         </is>
       </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>El estudiante está en el reporte oficial pero falta en la matriz del docente.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="25" customHeight="1">
-      <c r="A4" s="17" t="inlineStr">
-        <is>
-          <t>2BV</t>
-        </is>
-      </c>
-      <c r="B4" s="18" t="inlineStr">
-        <is>
-          <t>MENDOZA LIA SAMARA</t>
-        </is>
-      </c>
-      <c r="C4" s="17" t="inlineStr">
-        <is>
-          <t>⚠️ FALTA EN SISTEMA</t>
-        </is>
-      </c>
-      <c r="D4" s="18" t="inlineStr">
-        <is>
-          <t>El estudiante está en la matriz del docente pero no en el reporte oficial.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="15" t="inlineStr">
-        <is>
-          <t>2BV</t>
-        </is>
-      </c>
-      <c r="B5" s="16" t="inlineStr">
-        <is>
-          <t>MENDOZA VILLA LÍA SAMARA</t>
-        </is>
-      </c>
-      <c r="C5" s="15" t="inlineStr">
-        <is>
-          <t>⚠️ FALTA EN DOCENTE</t>
+      <c r="C5" s="17" t="inlineStr">
+        <is>
+          <t>(Nómina)</t>
         </is>
       </c>
       <c r="D5" s="16" t="inlineStr">
         <is>
-          <t>El estudiante está en el reporte oficial pero falta en la matriz del docente.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="25" customHeight="1">
-      <c r="A6" s="17" t="inlineStr">
-        <is>
-          <t>2BV</t>
-        </is>
-      </c>
-      <c r="B6" s="18" t="inlineStr">
-        <is>
-          <t>MIRANDA CHUISACA DYLAN YAHYR</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr">
-        <is>
-          <t>⚠️ DESFASE</t>
-        </is>
-      </c>
-      <c r="D6" s="18" t="inlineStr">
-        <is>
-          <t>Inconsistencia en la nómina del estudiante.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="25" customHeight="1">
-      <c r="A7" s="15" t="inlineStr">
-        <is>
-          <t>2BV</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>PEÑA GUIRACOCHA LADY ANAHY</t>
-        </is>
-      </c>
-      <c r="C7" s="15" t="inlineStr">
-        <is>
-          <t>⚠️ DESFASE</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr">
-        <is>
-          <t>Inconsistencia en la nómina del estudiante.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="25" customHeight="1">
-      <c r="A8" s="17" t="inlineStr">
-        <is>
-          <t>2BV</t>
-        </is>
-      </c>
-      <c r="B8" s="18" t="inlineStr">
-        <is>
-          <t>PULLA MAYORGA JORDY SEBASTIAN</t>
-        </is>
-      </c>
-      <c r="C8" s="17" t="inlineStr">
-        <is>
-          <t>⚠️ DESFASE</t>
-        </is>
-      </c>
-      <c r="D8" s="18" t="inlineStr">
-        <is>
-          <t>Inconsistencia en la nómina del estudiante.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="25" customHeight="1">
-      <c r="A9" s="15" t="inlineStr">
-        <is>
-          <t>2BV</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
-        <is>
-          <t>ROBLES LOAIZA ESTHER SOFIA</t>
-        </is>
-      </c>
-      <c r="C9" s="15" t="inlineStr">
-        <is>
-          <t>⚠️ DESFASE</t>
-        </is>
-      </c>
-      <c r="D9" s="16" t="inlineStr">
-        <is>
-          <t>Inconsistencia en la nómina del estudiante.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="25" customHeight="1">
-      <c r="A10" s="17" t="inlineStr">
-        <is>
-          <t>2BV</t>
-        </is>
-      </c>
-      <c r="B10" s="18" t="inlineStr">
-        <is>
-          <t>SAGBAY FAREZ ANDERSSON KALEB</t>
-        </is>
-      </c>
-      <c r="C10" s="17" t="inlineStr">
-        <is>
-          <t>⚠️ DESFASE</t>
-        </is>
-      </c>
-      <c r="D10" s="18" t="inlineStr">
-        <is>
-          <t>Inconsistencia en la nómina del estudiante.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="25" customHeight="1">
-      <c r="A11" s="15" t="inlineStr">
-        <is>
-          <t>2BV</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
-        <is>
-          <t>SIAVICHAY LEON JOSTIN JOSUE</t>
-        </is>
-      </c>
-      <c r="C11" s="15" t="inlineStr">
-        <is>
-          <t>⚠️ DESFASE</t>
-        </is>
-      </c>
-      <c r="D11" s="16" t="inlineStr">
-        <is>
-          <t>Inconsistencia en la nómina del estudiante.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="25" customHeight="1">
-      <c r="A12" s="17" t="inlineStr">
-        <is>
-          <t>2BV</t>
-        </is>
-      </c>
-      <c r="B12" s="18" t="inlineStr">
-        <is>
-          <t>SIBRI GUAPI JHOAN MATIAS</t>
-        </is>
-      </c>
-      <c r="C12" s="17" t="inlineStr">
-        <is>
-          <t>⚠️ DESFASE</t>
-        </is>
-      </c>
-      <c r="D12" s="18" t="inlineStr">
-        <is>
-          <t>Inconsistencia en la nómina del estudiante.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="25" customHeight="1">
-      <c r="A13" s="15" t="inlineStr">
-        <is>
-          <t>2BV</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
-        <is>
-          <t>SIBRI LATA JANINA ESTEFANIA</t>
-        </is>
-      </c>
-      <c r="C13" s="15" t="inlineStr">
-        <is>
-          <t>⚠️ DESFASE</t>
-        </is>
-      </c>
-      <c r="D13" s="16" t="inlineStr">
-        <is>
-          <t>Inconsistencia en la nómina del estudiante.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="25" customHeight="1">
-      <c r="A14" s="17" t="inlineStr">
-        <is>
-          <t>2BV</t>
-        </is>
-      </c>
-      <c r="B14" s="18" t="inlineStr">
-        <is>
-          <t>TADAY ORTIZ ABIGAIL ESTEFANIA</t>
-        </is>
-      </c>
-      <c r="C14" s="17" t="inlineStr">
-        <is>
-          <t>⚠️ DESFASE</t>
-        </is>
-      </c>
-      <c r="D14" s="18" t="inlineStr">
-        <is>
-          <t>Inconsistencia en la nómina del estudiante.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="25" customHeight="1">
-      <c r="A15" s="15" t="inlineStr">
-        <is>
-          <t>2BV</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
-        <is>
-          <t>TANGUILA RUIZ YESLY ELIZABETH</t>
-        </is>
-      </c>
-      <c r="C15" s="15" t="inlineStr">
-        <is>
-          <t>⚠️ DESFASE</t>
-        </is>
-      </c>
-      <c r="D15" s="16" t="inlineStr">
-        <is>
-          <t>Inconsistencia en la nómina del estudiante.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="25" customHeight="1">
-      <c r="A16" s="17" t="inlineStr">
-        <is>
-          <t>2BV</t>
-        </is>
-      </c>
-      <c r="B16" s="18" t="inlineStr">
-        <is>
-          <t>VALDEZ MONTESDEOCA ANGEL JOSUE</t>
-        </is>
-      </c>
-      <c r="C16" s="17" t="inlineStr">
-        <is>
-          <t>⚠️ DESFASE</t>
-        </is>
-      </c>
-      <c r="D16" s="18" t="inlineStr">
-        <is>
-          <t>Inconsistencia en la nómina del estudiante.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="25" customHeight="1">
-      <c r="A17" s="15" t="inlineStr">
-        <is>
-          <t>2BV</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="inlineStr">
-        <is>
-          <t>VIDAL PATIÑO EMMA ISABELLA</t>
-        </is>
-      </c>
-      <c r="C17" s="15" t="inlineStr">
-        <is>
-          <t>⚠️ DESFASE</t>
-        </is>
-      </c>
-      <c r="D17" s="16" t="inlineStr">
-        <is>
-          <t>Inconsistencia en la nómina del estudiante.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="25" customHeight="1">
-      <c r="A18" s="17" t="inlineStr">
-        <is>
-          <t>2BV</t>
-        </is>
-      </c>
-      <c r="B18" s="18" t="inlineStr">
-        <is>
-          <t>VIZHÑAY SOLIZ LUIS MATEO</t>
-        </is>
-      </c>
-      <c r="C18" s="17" t="inlineStr">
-        <is>
-          <t>⚠️ DESFASE</t>
-        </is>
-      </c>
-      <c r="D18" s="18" t="inlineStr">
-        <is>
-          <t>Inconsistencia en la nómina del estudiante.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="25" customHeight="1">
-      <c r="A19" s="15" t="inlineStr">
-        <is>
-          <t>2BV</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="inlineStr">
-        <is>
-          <t>ZHINDON ROBLES SNEYDER ALEXANDER</t>
-        </is>
-      </c>
-      <c r="C19" s="15" t="inlineStr">
-        <is>
-          <t>⚠️ DESFASE</t>
-        </is>
-      </c>
-      <c r="D19" s="16" t="inlineStr">
-        <is>
-          <t>Inconsistencia en la nómina del estudiante.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="25" customHeight="1">
-      <c r="A20" s="17" t="inlineStr">
-        <is>
-          <t>2BV</t>
-        </is>
-      </c>
-      <c r="B20" s="18" t="inlineStr">
-        <is>
-          <t>ZHUMILIMA CAMPOVERDE MILAGRO DEL CISNE</t>
-        </is>
-      </c>
-      <c r="C20" s="17" t="inlineStr">
-        <is>
-          <t>⚠️ DESFASE</t>
-        </is>
-      </c>
-      <c r="D20" s="18" t="inlineStr">
-        <is>
-          <t>Inconsistencia en la nómina del estudiante.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="25" customHeight="1">
-      <c r="A21" s="15" t="inlineStr">
-        <is>
-          <t>2BV</t>
-        </is>
-      </c>
-      <c r="B21" s="16" t="inlineStr">
-        <is>
-          <t>ÑAUTA BARRETO MATEO ARIEL</t>
-        </is>
-      </c>
-      <c r="C21" s="15" t="inlineStr">
-        <is>
-          <t>⚠️ DESFASE</t>
-        </is>
-      </c>
-      <c r="D21" s="16" t="inlineStr">
-        <is>
-          <t>Inconsistencia en la nómina del estudiante.</t>
+          <t>Falta</t>
+        </is>
+      </c>
+      <c r="E5" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A3:E3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
